--- a/现有全部对照品目录.xlsx
+++ b/现有全部对照品目录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\明\已上市品种变更项目\抓取标准物质信息\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DB277B-5C8E-473E-B7C2-9AEC6CF7DBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5812D214-1C86-48BB-8B1F-5CF66D96B15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +52,14 @@
   </si>
   <si>
     <t>rebalazole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐酸坦索罗辛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tamsulosin Hydrochloride</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -380,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -425,6 +433,23 @@
         <v>456</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>789</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1">
+        <v>101112</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/现有全部对照品目录.xlsx
+++ b/现有全部对照品目录.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\明\已上市品种变更项目\抓取标准物质信息\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5812D214-1C86-48BB-8B1F-5CF66D96B15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD1FC0D-71BF-4DFB-82E6-05AFD0E0AA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,20 +47,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>雷贝拉唑钠</t>
+    <t>Brivaracetam CRS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rebalazole</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>艾普拉唑磺酰化物</t>
+  </si>
+  <si>
+    <t>艾普拉唑</t>
   </si>
   <si>
     <t>盐酸坦索罗辛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tamsulosin Hydrochloride</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲磺酸多沙唑嗪</t>
+  </si>
+  <si>
+    <t>水杨酸片</t>
+  </si>
+  <si>
+    <t>美沙拉秦</t>
+  </si>
+  <si>
+    <t>水杨酸</t>
+  </si>
+  <si>
+    <t>羟苯丙酯</t>
+  </si>
+  <si>
+    <t>100565-202103</t>
+  </si>
+  <si>
+    <t>100909-202002</t>
+  </si>
+  <si>
+    <t>100106-202106</t>
+  </si>
+  <si>
+    <t>100908-202403</t>
+  </si>
+  <si>
+    <t>100688-202103</t>
+  </si>
+  <si>
+    <t>100566-202403</t>
+  </si>
+  <si>
+    <t>100444-202306</t>
+  </si>
+  <si>
+    <t>100908-202002</t>
+  </si>
+  <si>
+    <t>100103-202315</t>
   </si>
 </sst>
 </file>
@@ -112,7 +151,15 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -388,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -421,16 +468,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1">
-        <v>123</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E2" s="1">
-        <v>456</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -438,16 +485,208 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="C3" s="1">
-        <v>789</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="E3" s="1">
-        <v>101112</v>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/现有全部对照品目录.xlsx
+++ b/现有全部对照品目录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\明\已上市品种变更项目\抓取标准物质信息\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD1FC0D-71BF-4DFB-82E6-05AFD0E0AA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E922F5-8DF2-4D77-8785-C4498E7FE271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,18 +35,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对照品英文名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对照品中文批号Chp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对照品英文批号EP-USP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Brivaracetam CRS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -100,6 +92,30 @@
   </si>
   <si>
     <t>100103-202315</t>
+  </si>
+  <si>
+    <t>对照品英文名称EP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对照品英文批号EP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对照品英文名称USP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对照品英文批号USP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brivaracetam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -144,22 +160,14 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -435,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -443,10 +451,12 @@
     <col min="3" max="3" width="20.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="24.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -454,184 +464,196 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -639,10 +661,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -650,10 +672,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -661,10 +683,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -672,10 +694,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -683,10 +705,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/现有全部对照品目录.xlsx
+++ b/现有全部对照品目录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\明\已上市品种变更项目\抓取标准物质信息\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E922F5-8DF2-4D77-8785-C4498E7FE271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC8684E-E302-4226-8008-92060EEC0B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/现有全部对照品目录.xlsx
+++ b/现有全部对照品目录.xlsx
@@ -427,21 +427,15 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>艾普拉唑</v>
+        <v>艾普拉唑磺酰化物</v>
       </c>
       <c r="C2" t="str">
-        <v>100908-202002</v>
+        <v>100909-202002</v>
       </c>
       <c r="D2" t="str">
-        <v>Brivaracetam</v>
+        <v>Brivaracetam CRS</v>
       </c>
       <c r="E2" t="str">
-        <v>1.0</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Brivaracetam CRS</v>
-      </c>
-      <c r="G2" t="str">
         <v>1</v>
       </c>
     </row>
@@ -450,22 +444,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>水杨酸片</v>
+        <v>水杨酸</v>
       </c>
       <c r="C3" t="str">
-        <v>100103-202315</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Tamsulosin Hydrochloride</v>
-      </c>
-      <c r="E3" t="str">
-        <v>1</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Tamsulosin Hydrochloride</v>
-      </c>
-      <c r="G3" t="str">
-        <v>1.0</v>
+        <v>100106-202106</v>
       </c>
     </row>
     <row r="4">
@@ -473,10 +455,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>美沙拉秦</v>
+        <v>艾普拉唑</v>
       </c>
       <c r="C4" t="str">
-        <v>100565-202103</v>
+        <v>100908-202403</v>
       </c>
     </row>
     <row r="5">
@@ -484,10 +466,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>美沙拉秦</v>
+        <v>盐酸坦索罗辛</v>
       </c>
       <c r="C5" t="str">
-        <v>100565-202103</v>
+        <v>100688-202103</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +477,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>艾普拉唑磺酰化物</v>
+        <v>甲磺酸多沙唑嗪</v>
       </c>
       <c r="C6" t="str">
-        <v>100909-202002</v>
+        <v>100566-202403</v>
       </c>
     </row>
     <row r="7">
@@ -506,10 +488,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>艾普拉唑磺酰化物</v>
+        <v>羟苯丙酯</v>
       </c>
       <c r="C7" t="str">
-        <v>100909-202002</v>
+        <v>100444-202306</v>
       </c>
     </row>
     <row r="8">
@@ -517,10 +499,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>水杨酸</v>
+        <v>水杨酸片</v>
       </c>
       <c r="C8" t="str">
-        <v>100106-202106</v>
+        <v>100103-202416</v>
       </c>
     </row>
     <row r="9">
@@ -528,10 +510,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>艾普拉唑</v>
+        <v>伊曲康唑</v>
       </c>
       <c r="C9" t="str">
-        <v>100908-202403</v>
+        <v>100631-201402</v>
       </c>
     </row>
     <row r="10">
@@ -539,10 +521,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>艾普拉唑</v>
+        <v>伊曲康唑杂质A</v>
       </c>
       <c r="C10" t="str">
-        <v>100908-202403</v>
+        <v>130686-201501</v>
       </c>
     </row>
     <row r="11">
@@ -550,10 +532,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>艾普拉唑</v>
+        <v>伊曲康唑杂质B</v>
       </c>
       <c r="C11" t="str">
-        <v>100908-202403</v>
+        <v>130687-201501</v>
       </c>
     </row>
     <row r="12">
@@ -561,10 +543,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>盐酸坦索罗辛</v>
+        <v>伊曲康唑杂质C</v>
       </c>
       <c r="C12" t="str">
-        <v>100688-202103</v>
+        <v>130688-201501</v>
       </c>
     </row>
     <row r="13">
@@ -572,10 +554,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>甲磺酸多沙唑嗪</v>
+        <v>伊曲康唑杂质D</v>
       </c>
       <c r="C13" t="str">
-        <v>100566-202403</v>
+        <v>130689-201501</v>
       </c>
     </row>
     <row r="14">
@@ -583,10 +565,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>甲磺酸多沙唑嗪</v>
+        <v>伊曲康唑杂质E</v>
       </c>
       <c r="C14" t="str">
-        <v>100566-202403</v>
+        <v>130690-201501</v>
       </c>
     </row>
     <row r="15">
@@ -594,10 +576,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>甲磺酸多沙唑嗪</v>
+        <v>伊曲康唑杂质F</v>
       </c>
       <c r="C15" t="str">
-        <v>100566-202403</v>
+        <v>130691-201501</v>
       </c>
     </row>
     <row r="16">
@@ -605,65 +587,35 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>盐酸坦索罗辛</v>
+        <v>伊曲康唑杂质G</v>
       </c>
       <c r="C16" t="str">
-        <v>100688-202103</v>
+        <v>130692-201501</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>羟苯丙酯</v>
-      </c>
-      <c r="C17" t="str">
-        <v>100444-202306</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>甲磺酸多沙唑嗪</v>
-      </c>
-      <c r="C18" t="str">
-        <v>100566-202403</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>盐酸坦索罗辛</v>
-      </c>
-      <c r="C19" t="str">
-        <v>100688-202103</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>甲磺酸多沙唑嗪</v>
-      </c>
-      <c r="C20" t="str">
-        <v>100566-202403</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>盐酸坦索罗辛</v>
-      </c>
-      <c r="C21" t="str">
-        <v>100688-202103</v>
       </c>
     </row>
   </sheetData>

--- a/现有全部对照品目录.xlsx
+++ b/现有全部对照品目录.xlsx
@@ -1,46 +1,212 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\新建文件夹 (2)\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74892FE6-F30A-4199-8F50-B91D26843BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>对照品中文名称</t>
+  </si>
+  <si>
+    <t>对照品中文批号Chp</t>
+  </si>
+  <si>
+    <t>对照品英文名称EP</t>
+  </si>
+  <si>
+    <t>对照品英文批号EP</t>
+  </si>
+  <si>
+    <t>对照品英文名称USP</t>
+  </si>
+  <si>
+    <t>对照品英文批号USP</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>艾普拉唑磺酰化物</t>
+  </si>
+  <si>
+    <t>100909-202002</t>
+  </si>
+  <si>
+    <t>Brivaracetam CRS</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>水杨酸</t>
+  </si>
+  <si>
+    <t>100106-202106</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>艾普拉唑</t>
+  </si>
+  <si>
+    <t>100908-202403</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>盐酸坦索罗辛</t>
+  </si>
+  <si>
+    <t>100688-202103</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>甲磺酸多沙唑嗪</t>
+  </si>
+  <si>
+    <t>100566-202403</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>羟苯丙酯</t>
+  </si>
+  <si>
+    <t>100444-202306</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>伊曲康唑</t>
+  </si>
+  <si>
+    <t>100631-201402</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>伊曲康唑杂质A</t>
+  </si>
+  <si>
+    <t>130686-201501</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>伊曲康唑杂质B</t>
+  </si>
+  <si>
+    <t>130687-201501</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>伊曲康唑杂质C</t>
+  </si>
+  <si>
+    <t>130688-201501</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>伊曲康唑杂质D</t>
+  </si>
+  <si>
+    <t>130689-201501</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>伊曲康唑杂质E</t>
+  </si>
+  <si>
+    <t>130690-201501</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>伊曲康唑杂质F</t>
+  </si>
+  <si>
+    <t>130691-201501</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>伊曲康唑杂质G</t>
+  </si>
+  <si>
+    <t>130692-201501</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,13 +231,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,231 +570,234 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="15.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>序号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>对照品中文名称</v>
-      </c>
-      <c r="C1" t="str">
-        <v>对照品中文批号Chp</v>
-      </c>
-      <c r="D1" t="str">
-        <v>对照品英文名称EP</v>
-      </c>
-      <c r="E1" t="str">
-        <v>对照品英文批号EP</v>
-      </c>
-      <c r="F1" t="str">
-        <v>对照品英文名称USP</v>
-      </c>
-      <c r="G1" t="str">
-        <v>对照品英文批号USP</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
+    <row r="1" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>艾普拉唑磺酰化物</v>
-      </c>
-      <c r="C2" t="str">
-        <v>100909-202002</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Brivaracetam CRS</v>
-      </c>
-      <c r="E2" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>水杨酸</v>
-      </c>
-      <c r="C3" t="str">
-        <v>100106-202106</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>艾普拉唑</v>
-      </c>
-      <c r="C4" t="str">
-        <v>100908-202403</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>盐酸坦索罗辛</v>
-      </c>
-      <c r="C5" t="str">
-        <v>100688-202103</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>甲磺酸多沙唑嗪</v>
-      </c>
-      <c r="C6" t="str">
-        <v>100566-202403</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>羟苯丙酯</v>
-      </c>
-      <c r="C7" t="str">
-        <v>100444-202306</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
+    </row>
+    <row r="2" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>水杨酸片</v>
-      </c>
-      <c r="C8" t="str">
-        <v>100103-202416</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>伊曲康唑</v>
-      </c>
-      <c r="C9" t="str">
-        <v>100631-201402</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>伊曲康唑杂质A</v>
-      </c>
-      <c r="C10" t="str">
-        <v>130686-201501</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>伊曲康唑杂质B</v>
-      </c>
-      <c r="C11" t="str">
-        <v>130687-201501</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>伊曲康唑杂质C</v>
-      </c>
-      <c r="C12" t="str">
-        <v>130688-201501</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>伊曲康唑杂质D</v>
-      </c>
-      <c r="C13" t="str">
-        <v>130689-201501</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>伊曲康唑杂质E</v>
-      </c>
-      <c r="C14" t="str">
-        <v>130690-201501</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
+    </row>
+    <row r="4" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>伊曲康唑杂质F</v>
-      </c>
-      <c r="C15" t="str">
-        <v>130691-201501</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>伊曲康唑杂质G</v>
-      </c>
-      <c r="C16" t="str">
-        <v>130692-201501</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
+    <row r="5" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
+    <row r="6" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
+    <ignoredError sqref="A1:G7 A17:G21 A8 D8:G8 A9:A15 D9:G15 A16 D16:G16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>